--- a/output/pdf_financials_xlsx/ARK.xlsx
+++ b/output/pdf_financials_xlsx/ARK.xlsx
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.923051</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.416205</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.67058</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.790055</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.986993</v>
       </c>
     </row>
     <row r="93">
@@ -4123,7 +4123,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>0.923051</v>
       </c>

--- a/output/pdf_financials_xlsx/ARK.xlsx
+++ b/output/pdf_financials_xlsx/ARK.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.1e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000478</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.07391300000000001</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.035167</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.206938</v>
       </c>
     </row>
     <row r="13">
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-5.945556</v>
+        <v>-5.945567</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.717894</v>
+        <v>-5.718372</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.22275</v>
+        <v>-2.296663</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-10.956563</v>
+        <v>-10.99173</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-10.956563</v>
+        <v>-11.163501</v>
       </c>
     </row>
     <row r="28">
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.923889</v>
+        <v>-5.9239</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.629492</v>
+        <v>-5.62997</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.102538</v>
+        <v>-2.176451</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-10.832696</v>
+        <v>-10.867863</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-10.829871</v>
+        <v>-11.036809</v>
       </c>
     </row>
     <row r="30">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">

--- a/output/pdf_financials_xlsx/ARK.xlsx
+++ b/output/pdf_financials_xlsx/ARK.xlsx
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.040559</v>
+        <v>0.348568</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.125266</v>
+        <v>0.433462</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.07395599999999999</v>
+        <v>0.288984</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.190959</v>
+        <v>1.335213</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.200732</v>
+        <v>0.5052759999999999</v>
       </c>
     </row>
     <row r="8">
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.040559</v>
+        <v>0.348568</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.125266</v>
+        <v>0.433462</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.07395599999999999</v>
+        <v>0.288984</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.190959</v>
+        <v>1.335213</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.200732</v>
+        <v>0.5052759999999999</v>
       </c>
     </row>
     <row r="11">
@@ -6813,7 +6813,11 @@
           <t>Directors’ fees 12,14</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -9127,7 +9131,11 @@
           <t>Directors’ fees 12,14</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E144" s="5" t="n">
         <v>0.308009</v>
       </c>
